--- a/data/trans_orig/Hacinamiento_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18128</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95778</t>
+          <t>95422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103688</t>
+          <t>103040</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104873</t>
+          <t>105892</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113982</t>
+          <t>114445</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>205371</t>
+          <t>204491</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215810</t>
+          <t>215912</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13985</t>
+          <t>13470</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>17919</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13832</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28214</t>
+          <t>27132</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>110327</t>
+          <t>110842</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>119233</t>
+          <t>119790</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>123833</t>
+          <t>122823</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134055</t>
+          <t>134024</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>236839</t>
+          <t>237921</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>251221</t>
+          <t>251331</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12473</t>
+          <t>13325</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20944</t>
+          <t>21306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>94060</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103458</t>
+          <t>103377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101182</t>
+          <t>100874</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109672</t>
+          <t>109263</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>199014</t>
+          <t>198652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>210754</t>
+          <t>210901</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>19111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24280</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20781</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37911</t>
+          <t>38764</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146601</t>
+          <t>146225</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>157876</t>
+          <t>158126</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>132666</t>
+          <t>133572</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145686</t>
+          <t>145923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>284371</t>
+          <t>283518</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>301501</t>
+          <t>301169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25409</t>
+          <t>24919</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43683</t>
+          <t>42812</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33619</t>
+          <t>32699</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53681</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61797</t>
+          <t>61541</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89101</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>458560</t>
+          <t>459431</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476834</t>
+          <t>477324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>474868</t>
+          <t>475175</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>494930</t>
+          <t>495850</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>941691</t>
+          <t>941872</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>968995</t>
+          <t>969251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14448</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14794</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11314</t>
+          <t>10925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24284</t>
+          <t>24200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82681</t>
+          <t>82813</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92475</t>
+          <t>92841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97707</t>
+          <t>97297</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>107445</t>
+          <t>107638</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185345</t>
+          <t>185429</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>198315</t>
+          <t>198704</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>9827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20933</t>
+          <t>21274</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19170</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>19646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35595</t>
+          <t>35616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108050</t>
+          <t>107709</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>119262</t>
+          <t>119156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135386</t>
+          <t>135955</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>147136</t>
+          <t>146775</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>247944</t>
+          <t>247923</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>263565</t>
+          <t>263893</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>22379</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>21910</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23375</t>
+          <t>23097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39630</t>
+          <t>40184</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82961</t>
+          <t>82472</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94701</t>
+          <t>94618</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94317</t>
+          <t>94874</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106966</t>
+          <t>107189</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182004</t>
+          <t>181450</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198259</t>
+          <t>198537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>16791</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19282</t>
+          <t>19643</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>16147</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31684</t>
+          <t>32677</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129762</t>
+          <t>129211</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140497</t>
+          <t>140649</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135659</t>
+          <t>135298</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147404</t>
+          <t>147135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>269259</t>
+          <t>268266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>284822</t>
+          <t>284796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>39011</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61454</t>
+          <t>60340</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39493</t>
+          <t>38238</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62706</t>
+          <t>61357</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83350</t>
+          <t>83051</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114106</t>
+          <t>113810</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>415511</t>
+          <t>416625</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>438576</t>
+          <t>437954</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>476075</t>
+          <t>477424</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>499288</t>
+          <t>500543</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>901640</t>
+          <t>901936</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>932396</t>
+          <t>932695</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>12794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>27451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74806</t>
+          <t>74623</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84811</t>
+          <t>84867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89728</t>
+          <t>89410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99913</t>
+          <t>99783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168767</t>
+          <t>167308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>182231</t>
+          <t>181965</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17728</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>16574</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15294</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30917</t>
+          <t>30931</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>134199</t>
+          <t>134153</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>144644</t>
+          <t>144612</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>159736</t>
+          <t>158729</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>170015</t>
+          <t>169628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296313</t>
+          <t>296299</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>311936</t>
+          <t>311927</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17918</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15229</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15287</t>
+          <t>14722</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29170</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98634</t>
+          <t>98268</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>109047</t>
+          <t>108933</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117618</t>
+          <t>117106</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127483</t>
+          <t>127823</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220229</t>
+          <t>219646</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>234112</t>
+          <t>234677</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15369</t>
+          <t>15892</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14293</t>
+          <t>13710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29118</t>
+          <t>28425</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148497</t>
+          <t>148248</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159515</t>
+          <t>159619</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142194</t>
+          <t>141671</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152398</t>
+          <t>152485</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>294566</t>
+          <t>295259</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>309391</t>
+          <t>309974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34963</t>
+          <t>34721</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56558</t>
+          <t>55716</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28904</t>
+          <t>28628</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49272</t>
+          <t>48785</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70008</t>
+          <t>67923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99045</t>
+          <t>96114</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>468127</t>
+          <t>468969</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>489722</t>
+          <t>489964</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>521115</t>
+          <t>521602</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>541483</t>
+          <t>541759</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>996027</t>
+          <t>998958</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1025064</t>
+          <t>1027149</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>10701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18135</t>
+          <t>18232</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103924</t>
+          <t>104470</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112779</t>
+          <t>112798</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129180</t>
+          <t>128833</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137566</t>
+          <t>137414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>237448</t>
+          <t>237351</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>248624</t>
+          <t>248847</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12478</t>
+          <t>12531</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31138</t>
+          <t>30568</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21979</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43261</t>
+          <t>44650</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>170533</t>
+          <t>170682</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181743</t>
+          <t>181395</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>223516</t>
+          <t>224086</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>242176</t>
+          <t>242123</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>399305</t>
+          <t>397916</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>420587</t>
+          <t>421094</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>17216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12311</t>
+          <t>11773</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27593</t>
+          <t>28436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39243</t>
+          <t>40057</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173040</t>
+          <t>172763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>185030</t>
+          <t>184805</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156390</t>
+          <t>155547</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>171672</t>
+          <t>172210</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>334719</t>
+          <t>333905</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>353960</t>
+          <t>353917</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8209</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19898</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>11356</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25011</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>22392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40921</t>
+          <t>39790</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>147329</t>
+          <t>147990</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158975</t>
+          <t>159018</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156227</t>
+          <t>154774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170449</t>
+          <t>169882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>307545</t>
+          <t>308676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>325970</t>
+          <t>326074</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>29505</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51536</t>
+          <t>50292</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49592</t>
+          <t>49117</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77792</t>
+          <t>77960</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85519</t>
+          <t>86545</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>123106</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>608753</t>
+          <t>609997</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>630301</t>
+          <t>630784</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>682496</t>
+          <t>682328</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>710696</t>
+          <t>711171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1300330</t>
+          <t>1297471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1335058</t>
+          <t>1334032</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Hacinamiento_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7577</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4082</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12611</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,66%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4904</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2169</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9787</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2134</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10228</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,66%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7577</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3844</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12397</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>8079</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19008</t>
+          <t>19078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>110712</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>105678</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>114207</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,59%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,34%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>100305</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>95422</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>103040</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>94981</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>103075</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,34%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>110712</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>105892</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>114445</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,59%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>204491</t>
+          <t>204421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215912</t>
+          <t>215420</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11379</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6767</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17342</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>8364</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4522</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13470</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4616</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13737</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,73%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11379</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6718</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17919</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>14357</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27132</t>
+          <t>28406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>129363</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>123400</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>133975</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>115948</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>110842</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>119790</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>110575</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>119696</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,27%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>129363</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>122823</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>134024</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,92%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>237921</t>
+          <t>236647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>251331</t>
+          <t>250696</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>124312</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>124312</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>124312</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6631</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11295</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7588</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4008</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13325</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4190</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,07%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6631</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3310</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11699</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21306</t>
+          <t>21213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>105942</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>101278</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>109301</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,97%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,09%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>99797</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>94060</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>103377</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>94522</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>103195</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,93%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,59%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>105942</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>100874</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>109263</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>198652</t>
+          <t>198745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>210901</t>
+          <t>210571</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>107385</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>107385</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>107385</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16564</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11340</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23836</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>12105</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7210</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19111</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7506</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19852</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,56%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>16564</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>11023</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>23374</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21113</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38764</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>140382</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>133110</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>145606</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,81%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>153231</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>146225</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>158126</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>145484</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>157830</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>140382</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>133572</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>145923</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,45%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>283518</t>
+          <t>284124</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>301169</t>
+          <t>301743</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33274</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>52542</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>32961</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>24919</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>42812</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>24916</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>42840</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>6,56%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>4,96%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>42151</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>32699</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>53374</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61541</t>
+          <t>61548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88920</t>
+          <t>88815</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -2208,74 +2208,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>486398</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>476007</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>495275</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,06%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,7%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>696</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>469282</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>459431</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>477324</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>459403</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>477327</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>93,44%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>91,47%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>95,04%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>486398</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>475175</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>495850</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,03%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>89,9%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>93,81%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1425</t>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>941872</t>
+          <t>941977</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>969251</t>
+          <t>969244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>744</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>502243</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>502243</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>502243</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8687</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4716</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14677</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>8451</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4288</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14316</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4346</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14400</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,7%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,74%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8687</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4863</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15204</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10925</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>24737</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>103814</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>97824</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>107785</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,28%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88678</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>82813</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>92841</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>82729</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>92783</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,3%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,26%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>103814</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>97297</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>107638</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,28%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185429</t>
+          <t>184892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>198704</t>
+          <t>198132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12243</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7009</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18658</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>14676</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9827</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21274</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9368</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21134</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>11,38%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12243</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7781</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18601</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,92%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19646</t>
+          <t>19324</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35616</t>
+          <t>35110</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>142313</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>135898</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>147547</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,08%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>114307</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>107709</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>119156</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>107849</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>119615</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,62%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>142313</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>135955</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>146775</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,08%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>247923</t>
+          <t>248429</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>263893</t>
+          <t>264215</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3361,67 +3361,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>15479</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10069</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22098</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>15421</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10233</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22379</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10177</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21586</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>14,71%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,34%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15479</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9595</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>21910</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,25%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>23238</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40184</t>
+          <t>40748</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>101305</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>94686</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>106715</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,75%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>89430</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>82472</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>94618</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>83265</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>94674</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>85,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>78,66%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>90,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>101305</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>94874</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>107189</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,75%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>181450</t>
+          <t>180886</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198537</t>
+          <t>198396</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12978</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7595</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19340</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9942</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5353</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16791</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5879</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16063</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,81%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12978</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7806</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19643</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16147</t>
+          <t>15832</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32677</t>
+          <t>31442</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>141963</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>135601</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>147346</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>136060</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>129211</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>140649</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>129939</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>140123</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,19%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>141963</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>135298</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>147135</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,62%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>268266</t>
+          <t>269501</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>284796</t>
+          <t>285111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4047,67 +4047,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>49386</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>38616</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>62296</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>48489</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>39011</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>60340</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>59783</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>10,17%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>49386</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>38238</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>61357</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83051</t>
+          <t>84091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113810</t>
+          <t>114490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>489395</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>476485</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>500165</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>619</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>428476</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>416625</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>437954</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>417182</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>439163</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>89,83%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,82%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>489395</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>477424</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>500543</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,83%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>901936</t>
+          <t>901256</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>932695</t>
+          <t>931655</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8994</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4746</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14858</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9516</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5218</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15462</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5032</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15357</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10,56%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,79%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8994</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4891</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15264</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27451</t>
+          <t>26295</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>95680</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>89816</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>99928</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,8%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>80569</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>74623</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>84867</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>74728</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>85053</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>89,44%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,84%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,21%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>95680</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>89410</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>99783</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,41%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>167308</t>
+          <t>168464</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181965</t>
+          <t>182478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9653</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5679</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15974</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11666</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7315</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17774</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7322</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>17994</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,68%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,7%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9653</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5675</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16574</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15303</t>
+          <t>15121</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30931</t>
+          <t>29042</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>165650</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>159329</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>169624</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>140261</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>134153</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>144612</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>133933</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>144605</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,32%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,3%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,19%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>165650</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>158729</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>169628</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,49%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296299</t>
+          <t>298188</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>311927</t>
+          <t>312109</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9564</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5321</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16334</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,2%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>12304</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7619</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18284</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7701</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18400</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,56%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9564</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5024</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15741</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14722</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29753</t>
+          <t>30151</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>123283</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>116513</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>127526</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,8%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,99%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>104248</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>98268</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>108933</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>98152</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>108851</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,44%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>123283</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>117106</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>127823</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,8%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>219646</t>
+          <t>219248</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>234677</t>
+          <t>234083</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9535</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5132</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15664</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11237</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6502</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17873</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6699</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18055</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,76%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9535</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5078</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15892</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>14154</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28425</t>
+          <t>29453</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>148028</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>141899</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>152431</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,95%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,06%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>154884</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>148248</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>159619</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>148066</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>159422</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,24%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>148028</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>141671</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>152485</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,95%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>295259</t>
+          <t>294231</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>309974</t>
+          <t>309530</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>157563</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>157563</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>157563</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166121</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166121</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166121</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>157563</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>157563</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>157563</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>37745</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28893</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>48170</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>44723</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>34721</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>55716</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>34354</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>55005</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,52%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>37745</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>28628</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>48785</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67923</t>
+          <t>69808</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96114</t>
+          <t>97438</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>532642</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>522217</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>541494</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,38%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,55%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,93%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>722</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>479962</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>468969</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>489964</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>469680</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>490331</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,48%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>532642</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>521602</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>541759</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,38%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>998958</t>
+          <t>997634</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1027149</t>
+          <t>1025264</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>570387</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>570387</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>570387</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>789</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>524685</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>524685</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>524685</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>824</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>570387</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>570387</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>570387</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5600</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11448</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5288</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2373</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10701</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>11959</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18232</t>
+          <t>18175</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>120306</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>114458</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>123093</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>109883</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>104470</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>112798</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>134118</t>
+          <t>112669</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>128833</t>
+          <t>106369</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137414</t>
+          <t>115971</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>244000</t>
+          <t>232976</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>237351</t>
+          <t>226060</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>248847</t>
+          <t>237678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>115171</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>115171</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>115171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>118328</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>118328</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>118328</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>255583</t>
+          <t>244235</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>255583</t>
+          <t>244235</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>255583</t>
+          <t>244235</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17645</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27090</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,44%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10807</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6517</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17230</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19845</t>
+          <t>9552</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30568</t>
+          <t>14777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30651</t>
+          <t>27198</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>19450</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44650</t>
+          <t>38671</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>219248</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>209803</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>225792</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,56%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>177105</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>170682</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>181395</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,25%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,83%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>234809</t>
+          <t>172043</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>224086</t>
+          <t>166818</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>242123</t>
+          <t>175849</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>411915</t>
+          <t>391290</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>397916</t>
+          <t>379817</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>421094</t>
+          <t>399038</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>236893</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>236893</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>236893</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>187912</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>187912</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>187912</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>254654</t>
+          <t>181595</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>254654</t>
+          <t>181595</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>254654</t>
+          <t>181595</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>442566</t>
+          <t>418488</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>442566</t>
+          <t>418488</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>442566</t>
+          <t>418488</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15894</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10274</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23816</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10232</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5174</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17216</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18870</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11773</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28436</t>
+          <t>16027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29102</t>
+          <t>25986</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20045</t>
+          <t>18957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40057</t>
+          <t>34636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>151110</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>143188</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>156730</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,74%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,85%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>179747</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>172763</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>184805</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>94,61%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>165113</t>
+          <t>146591</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155547</t>
+          <t>140656</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>172210</t>
+          <t>150859</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>344860</t>
+          <t>297702</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>333905</t>
+          <t>289052</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>353917</t>
+          <t>304731</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167004</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167004</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167004</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189979</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189979</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189979</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183983</t>
+          <t>156683</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183983</t>
+          <t>156683</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183983</t>
+          <t>156683</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>373962</t>
+          <t>323688</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>373962</t>
+          <t>323688</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>373962</t>
+          <t>323688</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15775</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10177</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22858</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>13110</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8209</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19237</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17078</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26464</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>30109</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22392</t>
+          <t>21773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39790</t>
+          <t>39576</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>153601</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>146518</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>159199</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>86,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>154117</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>147990</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>159018</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,16%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>164160</t>
+          <t>152095</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154774</t>
+          <t>144905</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>169882</t>
+          <t>156536</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>318278</t>
+          <t>305696</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>308676</t>
+          <t>296229</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>326074</t>
+          <t>314032</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167227</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167227</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167227</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166429</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166429</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166429</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>348466</t>
+          <t>335805</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>348466</t>
+          <t>335805</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348466</t>
+          <t>335805</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>54913</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>42903</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>69325</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29505</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>50292</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>62086</t>
+          <t>39637</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49117</t>
+          <t>30673</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77960</t>
+          <t>51187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,17 +8011,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>101524</t>
+          <t>94550</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86545</t>
+          <t>79571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123106</t>
+          <t>113243</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>644266</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>629854</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>656276</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,08%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>874</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>620851</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>609997</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>630784</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>94,03%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>698202</t>
+          <t>583399</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>682328</t>
+          <t>571849</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>711171</t>
+          <t>592363</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,17 +8124,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1319053</t>
+          <t>1227665</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1297471</t>
+          <t>1208972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1334032</t>
+          <t>1242644</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699179</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699179</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699179</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>936</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>660289</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>660289</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>660289</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>974</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760288</t>
+          <t>623036</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760288</t>
+          <t>623036</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760288</t>
+          <t>623036</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1420577</t>
+          <t>1322215</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1420577</t>
+          <t>1322215</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1420577</t>
+          <t>1322215</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
